--- a/NB Financial Model.xlsx
+++ b/NB Financial Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1031d5e88fe9b877/Stock Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="8_{A552A25C-35E5-1D4B-8D76-F2809CEF67ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE5333B-929B-3A4C-B257-0945EC380259}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="8_{A552A25C-35E5-1D4B-8D76-F2809CEF67ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CE088D6-A18F-7F4E-ACDF-D8D855018DED}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19580" activeTab="1" xr2:uid="{B7360AAF-28EE-334A-A571-E3EC8B03412C}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Model" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -600,11 +600,11 @@
     <v>Powered by Refinitiv</v>
     <v>12.58</v>
     <v>2.17</v>
-    <v>0.1903</v>
-    <v>-0.28999999999999998</v>
-    <v>-5.9062999999999997E-2</v>
-    <v>0.08</v>
-    <v>1.7316000000000002E-2</v>
+    <v>0.21199999999999999</v>
+    <v>0.02</v>
+    <v>4.3959999999999997E-3</v>
+    <v>5.5800000000000002E-2</v>
+    <v>1.221E-2</v>
     <v>USD</v>
     <v>NioCorp Developments Ltd. is developing the Elk Creek Project that is expected to produce niobium, scandium, and titanium. The Company is also evaluating the potential to produce several rare earths from the Elk Creek Project. The Elk Creek Project is a shovel-ready pure-play critical minerals project with the highest-grade Niobium resource in North America and an indicated rare earth resource in the United States. The Elk Creek Project is located approximately 105 kilometers (kms) southeast of Lincoln, Nebraska (the state capital); 129 kms south of Omaha, Nebraska, and three miles west of Elk Creek, Nebraska and six miles south of Tecumseh, Nebraska.</v>
     <v>7</v>
@@ -612,25 +612,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>7000 S Yosemite St Ste 115, CENTENNIAL, CO, 80112-2004 US</v>
-    <v>4.8899999999999997</v>
+    <v>4.59</v>
     <v>Metals &amp; Mining</v>
     <v>Stock</v>
-    <v>46197.997960439061</v>
+    <v>46202.977165034376</v>
     <v>0</v>
-    <v>4.53</v>
-    <v>672612402</v>
+    <v>4.28</v>
+    <v>665333047</v>
     <v>NioCorp Developments Ltd.</v>
     <v>NioCorp Developments Ltd.</v>
-    <v>4.83</v>
+    <v>4.4800000000000004</v>
     <v>0</v>
-    <v>4.91</v>
-    <v>4.62</v>
-    <v>4.7</v>
+    <v>4.55</v>
+    <v>4.57</v>
+    <v>4.6257999999999999</v>
     <v>145587100</v>
     <v>NB</v>
     <v>NioCorp Developments Ltd. (XNAS:NB)</v>
-    <v>3660234</v>
-    <v>3656295</v>
+    <v>3423411</v>
+    <v>3603081</v>
     <v>1987</v>
   </rv>
   <rv s="2">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B2" s="1" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">_FV(A1,"Price")</f>
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B4" s="1" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">_FV(A1,"Market cap",TRUE)/1000000</f>
-        <v>672.61240199999997</v>
+        <v>665.33304699999997</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B7" s="4">
         <f ca="1">B4+B6-B5</f>
-        <v>672.61240199999997</v>
+        <v>665.33304699999997</v>
       </c>
     </row>
     <row r="28" spans="3:3" x14ac:dyDescent="0.2">
@@ -2318,27 +2318,27 @@
         <v>44</v>
       </c>
       <c r="C33" s="11">
-        <f>SUM(C6:F6)</f>
+        <f t="shared" ref="C33:C43" si="0">SUM(C6:F6)</f>
         <v>0</v>
       </c>
       <c r="D33" s="11">
-        <f>SUM(G6:J6)</f>
+        <f t="shared" ref="D33:D43" si="1">SUM(G6:J6)</f>
         <v>0</v>
       </c>
       <c r="E33" s="14">
-        <f>SUM(K6:N6)</f>
+        <f t="shared" ref="E33:E43" si="2">SUM(K6:N6)</f>
         <v>0</v>
       </c>
       <c r="F33" s="11">
-        <f>SUM(O6:R6)</f>
+        <f t="shared" ref="F33:F43" si="3">SUM(O6:R6)</f>
         <v>0</v>
       </c>
       <c r="G33" s="11">
-        <f>SUM(S6:V6)</f>
+        <f t="shared" ref="G33:G43" si="4">SUM(S6:V6)</f>
         <v>0</v>
       </c>
       <c r="H33" s="11">
-        <f>SUM(W6:Z6)</f>
+        <f t="shared" ref="H33:H43" si="5">SUM(W6:Z6)</f>
         <v>0</v>
       </c>
       <c r="I33" s="11">
@@ -2346,11 +2346,11 @@
         <v>0</v>
       </c>
       <c r="J33" s="11">
-        <f>SUM(AE6:AH6)</f>
+        <f t="shared" ref="J33:J43" si="6">SUM(AE6:AH6)</f>
         <v>0</v>
       </c>
       <c r="K33" s="11">
-        <f>SUM(AI6:AL6)</f>
+        <f t="shared" ref="K33:K43" si="7">SUM(AI6:AL6)</f>
         <v>0</v>
       </c>
     </row>
@@ -2359,39 +2359,39 @@
         <v>45</v>
       </c>
       <c r="C34" s="11">
-        <f>SUM(C7:F7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D34" s="11">
-        <f>SUM(G7:J7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E34" s="14">
-        <f>SUM(K7:N7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F34" s="11">
-        <f>SUM(O7:R7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G34" s="11">
-        <f>SUM(S7:V7)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H34" s="11">
-        <f>SUM(W7:Z7)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I34" s="11">
-        <f>SUM(W7:Z7)</f>
+        <f t="shared" ref="I34:I43" si="8">SUM(W7:Z7)</f>
         <v>0</v>
       </c>
       <c r="J34" s="11">
-        <f>SUM(AE7:AH7)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K34" s="11">
-        <f>SUM(AI7:AL7)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2400,39 +2400,39 @@
         <v>46</v>
       </c>
       <c r="C35" s="11">
-        <f>SUM(C8:F8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D35" s="11">
-        <f>SUM(G8:J8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E35" s="14">
-        <f>SUM(K8:N8)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F35" s="11">
-        <f>SUM(O8:R8)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G35" s="11">
-        <f>SUM(S8:V8)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H35" s="11">
-        <f>SUM(W8:Z8)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I35" s="11">
-        <f>SUM(W8:Z8)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J35" s="11">
-        <f>SUM(AE8:AH8)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K35" s="11">
-        <f>SUM(AI8:AL8)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2441,39 +2441,39 @@
         <v>47</v>
       </c>
       <c r="C36" s="11">
-        <f>SUM(C9:F9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D36" s="11">
-        <f>SUM(G9:J9)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E36" s="14">
-        <f>SUM(K9:N9)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F36" s="11">
-        <f>SUM(O9:R9)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G36" s="11">
-        <f>SUM(S9:V9)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H36" s="11">
-        <f>SUM(W9:Z9)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I36" s="11">
-        <f>SUM(W9:Z9)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J36" s="11">
-        <f>SUM(AE9:AH9)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K36" s="11">
-        <f>SUM(AI9:AL9)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2482,39 +2482,39 @@
         <v>48</v>
       </c>
       <c r="C37" s="11">
-        <f>SUM(C10:F10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D37" s="11">
-        <f>SUM(G10:J10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E37" s="14">
-        <f>SUM(K10:N10)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F37" s="11">
-        <f>SUM(O10:R10)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G37" s="11">
-        <f>SUM(S10:V10)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H37" s="11">
-        <f>SUM(W10:Z10)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I37" s="11">
-        <f>SUM(W10:Z10)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J37" s="11">
-        <f>SUM(AE10:AH10)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K37" s="11">
-        <f>SUM(AI10:AL10)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2523,39 +2523,39 @@
         <v>49</v>
       </c>
       <c r="C38" s="11">
-        <f>SUM(C11:F11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D38" s="11">
-        <f>SUM(G11:J11)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E38" s="14">
-        <f>SUM(K11:N11)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F38" s="11">
-        <f>SUM(O11:R11)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G38" s="11">
-        <f>SUM(S11:V11)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H38" s="11">
-        <f>SUM(W11:Z11)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I38" s="11">
-        <f>SUM(W11:Z11)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J38" s="11">
-        <f>SUM(AE11:AH11)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K38" s="11">
-        <f>SUM(AI11:AL11)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2564,39 +2564,39 @@
         <v>50</v>
       </c>
       <c r="C39" s="11">
-        <f>SUM(C12:F12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D39" s="11">
-        <f>SUM(G12:J12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E39" s="14">
-        <f>SUM(K12:N12)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F39" s="11">
-        <f>SUM(O12:R12)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G39" s="11">
-        <f>SUM(S12:V12)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H39" s="11">
-        <f>SUM(W12:Z12)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I39" s="11">
-        <f>SUM(W12:Z12)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J39" s="11">
-        <f>SUM(AE12:AH12)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K39" s="11">
-        <f>SUM(AI12:AL12)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2605,39 +2605,39 @@
         <v>51</v>
       </c>
       <c r="C40" s="11">
-        <f>SUM(C13:F13)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D40" s="11">
-        <f>SUM(G13:J13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E40" s="14">
-        <f>SUM(K13:N13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F40" s="11">
-        <f>SUM(O13:R13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G40" s="11">
-        <f>SUM(S13:V13)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H40" s="11">
-        <f>SUM(W13:Z13)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I40" s="11">
-        <f>SUM(W13:Z13)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J40" s="11">
-        <f>SUM(AE13:AH13)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K40" s="11">
-        <f>SUM(AI13:AL13)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2646,39 +2646,39 @@
         <v>52</v>
       </c>
       <c r="C41" s="11">
-        <f>SUM(C14:F14)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D41" s="11">
-        <f>SUM(G14:J14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E41" s="14">
-        <f>SUM(K14:N14)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F41" s="11">
-        <f>SUM(O14:R14)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G41" s="11">
-        <f>SUM(S14:V14)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H41" s="11">
-        <f>SUM(W14:Z14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I41" s="11">
-        <f>SUM(W14:Z14)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J41" s="11">
-        <f>SUM(AE14:AH14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K41" s="11">
-        <f>SUM(AI14:AL14)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M41" t="s">
@@ -2693,39 +2693,39 @@
         <v>53</v>
       </c>
       <c r="C42" s="11">
-        <f>SUM(C15:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D42" s="11">
-        <f>SUM(G15:J15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E42" s="14">
-        <f>SUM(K15:N15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F42" s="11">
-        <f>SUM(O15:R15)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G42" s="11">
-        <f>SUM(S15:V15)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H42" s="11">
-        <f>SUM(W15:Z15)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I42" s="11">
-        <f>SUM(W15:Z15)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J42" s="11">
-        <f>SUM(AE15:AH15)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K42" s="11">
-        <f>SUM(AI15:AL15)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M42" t="s">
@@ -2740,39 +2740,39 @@
         <v>54</v>
       </c>
       <c r="C43" s="11">
-        <f>SUM(C16:F16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D43" s="11">
-        <f>SUM(G16:J16)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E43" s="14">
-        <f>SUM(K16:N16)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F43" s="11">
-        <f>SUM(O16:R16)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G43" s="11">
-        <f>SUM(S16:V16)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H43" s="11">
-        <f>SUM(W16:Z16)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I43" s="11">
-        <f>SUM(W16:Z16)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J43" s="11">
-        <f>SUM(AE16:AH16)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K43" s="11">
-        <f>SUM(AI16:AL16)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L43" s="4"/>

--- a/NB Financial Model.xlsx
+++ b/NB Financial Model.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1031d5e88fe9b877/Stock Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E943F6E-F18C-0745-B7B2-2BD4FE2370C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0338EED0-366B-4493-8927-64B71CC460CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="37960" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="NAV" sheetId="3" r:id="rId2"/>
-    <sheet name="Valuation" sheetId="2" r:id="rId3"/>
-    <sheet name="Sensitivity" sheetId="4" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="5" r:id="rId2"/>
+    <sheet name="NAV" sheetId="3" r:id="rId3"/>
+    <sheet name="Valuation" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="115">
   <si>
     <t xml:space="preserve">Price </t>
   </si>
@@ -78,21 +77,12 @@
     <t>After-tax project NPV @ 8% ($M)</t>
   </si>
   <si>
-    <t>Company published figure (2022 FS). This already nets out the $1,141M capex on a 100%-equity basis.</t>
-  </si>
-  <si>
-    <t>(memo) Illustrative NPV from NAV sheet</t>
-  </si>
-  <si>
     <t>Initial capex to fund ($M)</t>
   </si>
   <si>
     <t>% funded by equity</t>
   </si>
   <si>
-    <t>ASSUMPTION. The rest is assumed debt / government loan. NioCorp has pursued large federal loan support; confirm actual mix from filings.</t>
-  </si>
-  <si>
     <t>% funded by debt / loan</t>
   </si>
   <si>
@@ -102,18 +92,12 @@
     <t>Assumed raise price ($/sh)</t>
   </si>
   <si>
-    <t>ASSUMPTION — defaults to current price. A capital raise of this size would likely price at a discount; lower it to stress dilution.</t>
-  </si>
-  <si>
     <t>New shares issued (M)</t>
   </si>
   <si>
     <t>Warrants + options (M)</t>
   </si>
   <si>
-    <t>UNVERIFIED — confirm SPAC warrant + option count from latest 10-Q.</t>
-  </si>
-  <si>
     <t>Fully diluted shares (M)</t>
   </si>
   <si>
@@ -153,9 +137,6 @@
     <t>Current price implies P/NAV of</t>
   </si>
   <si>
-    <t>Caveat: debt-funded capex avoids dilution but adds a future debt claim not modelled here; a precise levered case needs a debt-service schedule. Treat the equity-funded case as the conservative (max-dilution) bookend.</t>
-  </si>
-  <si>
     <t>Product</t>
   </si>
   <si>
@@ -177,9 +158,6 @@
     <t>Total LoM revenue</t>
   </si>
   <si>
-    <t>OPERATING &amp; CAPITAL (life of mine)</t>
-  </si>
-  <si>
     <t>Total operating cost</t>
   </si>
   <si>
@@ -207,9 +185,6 @@
     <t>Pre-production years</t>
   </si>
   <si>
-    <t>ANNUAL CASH FLOW  (flat-production simplification)</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
@@ -264,60 +239,9 @@
     <t>Illustrative project NPV (this flat model)</t>
   </si>
   <si>
-    <t>&lt;-- USE THE PUBLISHED $2,350M AS YOUR ANCHOR. This flat model is a transparent scaffold so you can see the mechanics and flex prices/discount rate; it ignores production ramp-up/down and depreciation-shield timing, so it will not exactly equal the company’s phased model.</t>
-  </si>
-  <si>
     <t>Flat model as % of published</t>
   </si>
   <si>
-    <t>Base Sc revenue ($M)</t>
-  </si>
-  <si>
-    <t>Base Ti revenue ($M)</t>
-  </si>
-  <si>
-    <t>Base opex ($M)</t>
-  </si>
-  <si>
-    <t>Tax rate</t>
-  </si>
-  <si>
-    <t>Sustaining ($M)</t>
-  </si>
-  <si>
-    <t>Initial capex ($M)</t>
-  </si>
-  <si>
-    <t>Closure ($M)</t>
-  </si>
-  <si>
-    <t>Prod years</t>
-  </si>
-  <si>
-    <t>Pre-prod years</t>
-  </si>
-  <si>
-    <t>Payable Nb (t)</t>
-  </si>
-  <si>
-    <t>FD shares (M)</t>
-  </si>
-  <si>
-    <t>Table 1 — Illustrative project NPV ($M):  Niobium price (cols) x Discount rate (rows)</t>
-  </si>
-  <si>
-    <t>Scandium &amp; titanium held at FS base prices. Closed-form annuity NPV consistent with the NAV sheet.</t>
-  </si>
-  <si>
-    <t>Disc \ Nb $/kg</t>
-  </si>
-  <si>
-    <t>Table 2 — Illustrative NAV per FD share ($):  same axes</t>
-  </si>
-  <si>
-    <t>Per-share table divides each NPV by current fully diluted share count (Valuation!B21) and is pre-P/NAV-discount. Scandium price is the bigger swing factor than niobium — build a second table on Sc price if that is your key risk.</t>
-  </si>
-  <si>
     <t>Input</t>
   </si>
   <si>
@@ -399,9 +323,6 @@
     <t>Project NAV</t>
   </si>
   <si>
-    <t>Corporate NAV per Share  (with financing / dilution)</t>
-  </si>
-  <si>
     <t>FINANCING OF INITIAL CAPITAL</t>
   </si>
   <si>
@@ -429,9 +350,6 @@
     <t>Mine life</t>
   </si>
   <si>
-    <t>Sensitivity Analysis</t>
-  </si>
-  <si>
     <t>Rev ($M)</t>
   </si>
   <si>
@@ -451,6 +369,21 @@
   </si>
   <si>
     <t>M shares</t>
+  </si>
+  <si>
+    <t>OPERATING &amp; CAPITAL</t>
+  </si>
+  <si>
+    <t>ANNUAL CASH FLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate NAV per Share  </t>
+  </si>
+  <si>
+    <t>NPV from NAV sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company published figure. </t>
   </si>
 </sst>
 </file>
@@ -467,7 +400,7 @@
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="#,##0.00;\(#,##0.00\);\-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -502,12 +435,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF595959"/>
@@ -515,25 +442,18 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -549,20 +469,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF0066CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -593,33 +513,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -627,45 +539,37 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -739,6 +643,10 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -950,25 +858,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="6" width="13.83203125" customWidth="1"/>
+    <col min="3" max="6" width="13.875" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="16.125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -976,7 +884,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -984,7 +892,7 @@
         <v>45.072000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -993,7 +901,7 @@
         <v>205.97904000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1001,7 +909,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +917,7 @@
         <v>14.66</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1018,10 +926,10 @@
         <v>195.13904000000002</v>
       </c>
     </row>
-    <row r="28" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="2"/>
     </row>
   </sheetData>
@@ -1031,18 +939,334 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="26"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="26"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="24">
+        <v>36655</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="24">
+        <v>38</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="24">
+        <v>4</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="24">
+        <v>171140</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="24">
+        <v>3676</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="24">
+        <v>431793</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="27">
+        <v>46.55</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="27">
+        <v>3674</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="27">
+        <v>0.99</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="27">
+        <v>195.94</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="24">
+        <v>1141</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="24">
+        <v>422</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="24">
+        <v>44</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="28">
+        <v>0.16420000000000001</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="28">
+        <v>0.08</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="24">
+        <v>2350</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="28">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="24">
+        <v>2800</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="28">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="27">
+        <f>Main!B5</f>
+        <v>25.5</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="24">
+        <f>(29985922+3020000)/1000000</f>
+        <v>33.005921999999998</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="24"/>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AS43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AR43"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.1640625" customWidth="1"/>
-    <col min="2" max="44" width="13.83203125" customWidth="1"/>
+    <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="44" width="13.875" customWidth="1"/>
     <col min="45" max="49" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1052,2939 +1276,2629 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="9">
+        <v>35</v>
+      </c>
+      <c r="B5" s="30">
         <f>Assumptions!$B$8</f>
         <v>171140</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="31">
         <f>Assumptions!$B$12</f>
         <v>46.55</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="13">
         <f>B5*C5/1000</f>
         <v>7966.5669999999991</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="15">
         <f>D5/$D$8</f>
         <v>0.36377572948079201</v>
       </c>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="9">
+        <v>36</v>
+      </c>
+      <c r="B6" s="30">
         <f>Assumptions!$B$9</f>
         <v>3676</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="31">
         <f>Assumptions!$B$13</f>
         <v>3674</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="13">
         <f>B6*C6/1000</f>
         <v>13505.624</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <f>D6/$D$8</f>
         <v>0.61670456329474066</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="9">
+        <v>37</v>
+      </c>
+      <c r="B7" s="30">
         <f>Assumptions!$B$10</f>
         <v>431793</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="31">
         <f>Assumptions!$B$14</f>
         <v>0.99</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="13">
         <f>B7*C7/1000</f>
         <v>427.47507000000002</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <f>D7/$D$8</f>
         <v>1.9519707224467282E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="20">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="13">
         <f>SUM(D5:D7)</f>
         <v>21899.666069999999</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="15">
         <f>D8/$D$8</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="10">
+        <v>39</v>
+      </c>
+      <c r="B11" s="8">
         <f>Assumptions!$B$16*Assumptions!$B$5/1000</f>
         <v>7182.1806999999999</v>
       </c>
-      <c r="C11" s="12"/>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="20">
+        <v>40</v>
+      </c>
+      <c r="B12" s="13">
         <f>D8-B11</f>
         <v>14717.485369999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="27">
+        <v>41</v>
+      </c>
+      <c r="B13" s="32">
         <f>Assumptions!$B$20</f>
         <v>0.16420000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="11">
+        <v>42</v>
+      </c>
+      <c r="B14" s="33">
         <f>Assumptions!$B$17</f>
         <v>1141</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="11">
+        <v>43</v>
+      </c>
+      <c r="B15" s="33">
         <f>Assumptions!$B$18</f>
         <v>422</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="11">
+        <v>44</v>
+      </c>
+      <c r="B16" s="33">
         <f>Assumptions!$B$19</f>
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="28">
+        <v>45</v>
+      </c>
+      <c r="B17" s="34">
         <f>Assumptions!$B$21</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="9">
+        <v>46</v>
+      </c>
+      <c r="B18" s="30">
         <f>Assumptions!$B$6</f>
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="9">
+        <v>47</v>
+      </c>
+      <c r="B19" s="30">
         <f>Assumptions!$B$7</f>
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="29"/>
-      <c r="X22" s="29"/>
-      <c r="Y22" s="29"/>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="29"/>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="29"/>
-      <c r="AE22" s="29"/>
-      <c r="AF22" s="29"/>
-      <c r="AG22" s="29"/>
-      <c r="AH22" s="29"/>
-      <c r="AI22" s="29"/>
-      <c r="AJ22" s="29"/>
-      <c r="AK22" s="29"/>
-      <c r="AL22" s="29"/>
-      <c r="AM22" s="29"/>
-      <c r="AN22" s="29"/>
-      <c r="AO22" s="29"/>
-      <c r="AP22" s="29"/>
-      <c r="AQ22" s="29"/>
-      <c r="AR22" s="29"/>
-      <c r="AS22" s="29"/>
-    </row>
-    <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="19"/>
+      <c r="AA22" s="19"/>
+      <c r="AB22" s="19"/>
+      <c r="AC22" s="19"/>
+      <c r="AD22" s="19"/>
+      <c r="AE22" s="19"/>
+      <c r="AF22" s="19"/>
+      <c r="AG22" s="19"/>
+      <c r="AH22" s="19"/>
+      <c r="AI22" s="19"/>
+      <c r="AJ22" s="19"/>
+      <c r="AK22" s="19"/>
+      <c r="AL22" s="19"/>
+      <c r="AM22" s="19"/>
+      <c r="AN22" s="19"/>
+      <c r="AO22" s="19"/>
+      <c r="AP22" s="19"/>
+      <c r="AQ22" s="19"/>
+      <c r="AR22" s="19"/>
+    </row>
+    <row r="23" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="30">
+        <v>48</v>
+      </c>
+      <c r="C23" s="20">
         <v>1</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="20">
         <v>2</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="20">
         <v>3</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="20">
         <v>4</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="20">
         <v>5</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="20">
         <v>6</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="20">
         <v>7</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="20">
         <v>8</v>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="20">
         <v>9</v>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="20">
         <v>10</v>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="20">
         <v>11</v>
       </c>
-      <c r="N23" s="30">
+      <c r="N23" s="20">
         <v>12</v>
       </c>
-      <c r="O23" s="30">
+      <c r="O23" s="20">
         <v>13</v>
       </c>
-      <c r="P23" s="30">
+      <c r="P23" s="20">
         <v>14</v>
       </c>
-      <c r="Q23" s="30">
+      <c r="Q23" s="20">
         <v>15</v>
       </c>
-      <c r="R23" s="30">
+      <c r="R23" s="20">
         <v>16</v>
       </c>
-      <c r="S23" s="30">
+      <c r="S23" s="20">
         <v>17</v>
       </c>
-      <c r="T23" s="30">
+      <c r="T23" s="20">
         <v>18</v>
       </c>
-      <c r="U23" s="30">
+      <c r="U23" s="20">
         <v>19</v>
       </c>
-      <c r="V23" s="30">
+      <c r="V23" s="20">
         <v>20</v>
       </c>
-      <c r="W23" s="30">
+      <c r="W23" s="20">
         <v>21</v>
       </c>
-      <c r="X23" s="30">
+      <c r="X23" s="20">
         <v>22</v>
       </c>
-      <c r="Y23" s="30">
+      <c r="Y23" s="20">
         <v>23</v>
       </c>
-      <c r="Z23" s="30">
+      <c r="Z23" s="20">
         <v>24</v>
       </c>
-      <c r="AA23" s="30">
+      <c r="AA23" s="20">
         <v>25</v>
       </c>
-      <c r="AB23" s="30">
+      <c r="AB23" s="20">
         <v>26</v>
       </c>
-      <c r="AC23" s="30">
+      <c r="AC23" s="20">
         <v>27</v>
       </c>
-      <c r="AD23" s="30">
+      <c r="AD23" s="20">
         <v>28</v>
       </c>
-      <c r="AE23" s="30">
+      <c r="AE23" s="20">
         <v>29</v>
       </c>
-      <c r="AF23" s="30">
+      <c r="AF23" s="20">
         <v>30</v>
       </c>
-      <c r="AG23" s="30">
+      <c r="AG23" s="20">
         <v>31</v>
       </c>
-      <c r="AH23" s="30">
+      <c r="AH23" s="20">
         <v>32</v>
       </c>
-      <c r="AI23" s="30">
+      <c r="AI23" s="20">
         <v>33</v>
       </c>
-      <c r="AJ23" s="30">
+      <c r="AJ23" s="20">
         <v>34</v>
       </c>
-      <c r="AK23" s="30">
+      <c r="AK23" s="20">
         <v>35</v>
       </c>
-      <c r="AL23" s="30">
+      <c r="AL23" s="20">
         <v>36</v>
       </c>
-      <c r="AM23" s="30">
+      <c r="AM23" s="20">
         <v>37</v>
       </c>
-      <c r="AN23" s="30">
+      <c r="AN23" s="20">
         <v>38</v>
       </c>
-      <c r="AO23" s="30">
+      <c r="AO23" s="20">
         <v>39</v>
       </c>
-      <c r="AP23" s="30">
+      <c r="AP23" s="20">
         <v>40</v>
       </c>
-      <c r="AQ23" s="30">
+      <c r="AQ23" s="20">
         <v>41</v>
       </c>
-      <c r="AR23" s="30">
+      <c r="AR23" s="20">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="J24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="K24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="L24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="M24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="O24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="P24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="R24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="S24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="T24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="U24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="V24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="W24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="X24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AH24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AM24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AN24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AO24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AP24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AQ24" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="AR24" s="31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="O24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="P24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="R24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="S24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="T24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="U24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="V24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="W24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="X24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AQ24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR24" s="21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="10">
+        <v>52</v>
+      </c>
+      <c r="C25" s="8">
         <f t="shared" ref="C25:AR25" si="0">IF(C23&gt;$B$19,$D$8/$B$18,0)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="8">
         <f>IF(G23&gt;$B$19,$D$8/$B$18,0)</f>
         <v>576.30700184210525</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="O25" s="10">
+      <c r="O25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="P25" s="10">
+      <c r="P25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="Q25" s="10">
+      <c r="Q25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="R25" s="10">
+      <c r="R25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="S25" s="10">
+      <c r="S25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="T25" s="10">
+      <c r="T25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="U25" s="10">
+      <c r="U25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="V25" s="10">
+      <c r="V25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="W25" s="10">
+      <c r="W25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="X25" s="10">
+      <c r="X25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="Y25" s="10">
+      <c r="Y25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="Z25" s="10">
+      <c r="Z25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AA25" s="10">
+      <c r="AA25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AB25" s="10">
+      <c r="AB25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AC25" s="10">
+      <c r="AC25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AD25" s="10">
+      <c r="AD25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AE25" s="10">
+      <c r="AE25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AF25" s="10">
+      <c r="AF25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AG25" s="10">
+      <c r="AG25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AH25" s="10">
+      <c r="AH25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AI25" s="10">
+      <c r="AI25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AJ25" s="10">
+      <c r="AJ25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AK25" s="10">
+      <c r="AK25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AL25" s="10">
+      <c r="AL25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AM25" s="10">
+      <c r="AM25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AN25" s="10">
+      <c r="AN25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AO25" s="10">
+      <c r="AO25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AP25" s="10">
+      <c r="AP25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AQ25" s="10">
+      <c r="AQ25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
-      <c r="AR25" s="10">
+      <c r="AR25" s="8">
         <f t="shared" si="0"/>
         <v>576.30700184210525</v>
       </c>
     </row>
-    <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="10">
+        <v>53</v>
+      </c>
+      <c r="C26" s="8">
         <f>IF(C23&gt;$B$19,-$B$11/$B$18,0)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <f t="shared" ref="D26:AR26" si="1">IF(D23&gt;$B$19,-$B$11/$B$18,0)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="Q26" s="10">
+      <c r="Q26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="R26" s="10">
+      <c r="R26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="S26" s="10">
+      <c r="S26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="T26" s="10">
+      <c r="T26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="U26" s="10">
+      <c r="U26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="V26" s="10">
+      <c r="V26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="W26" s="10">
+      <c r="W26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="X26" s="10">
+      <c r="X26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="Y26" s="10">
+      <c r="Y26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="Z26" s="10">
+      <c r="Z26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AA26" s="10">
+      <c r="AA26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AB26" s="10">
+      <c r="AB26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AC26" s="10">
+      <c r="AC26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AD26" s="10">
+      <c r="AD26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AE26" s="10">
+      <c r="AE26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AF26" s="10">
+      <c r="AF26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AG26" s="10">
+      <c r="AG26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AH26" s="10">
+      <c r="AH26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AI26" s="10">
+      <c r="AI26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AJ26" s="10">
+      <c r="AJ26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AK26" s="10">
+      <c r="AK26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AL26" s="10">
+      <c r="AL26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AM26" s="10">
+      <c r="AM26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AN26" s="10">
+      <c r="AN26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AO26" s="10">
+      <c r="AO26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AP26" s="10">
+      <c r="AP26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AQ26" s="10">
+      <c r="AQ26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
-      <c r="AR26" s="10">
+      <c r="AR26" s="8">
         <f t="shared" si="1"/>
         <v>-189.0047552631579</v>
       </c>
     </row>
-    <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="10">
+        <v>54</v>
+      </c>
+      <c r="C27" s="8">
         <f t="shared" ref="C27:AR27" si="2">C25+C26</f>
         <v>0</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="O27" s="10">
+      <c r="O27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="Q27" s="10">
+      <c r="Q27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="R27" s="10">
+      <c r="R27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="S27" s="10">
+      <c r="S27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="T27" s="10">
+      <c r="T27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="U27" s="10">
+      <c r="U27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="V27" s="10">
+      <c r="V27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="W27" s="10">
+      <c r="W27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="X27" s="10">
+      <c r="X27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="Y27" s="10">
+      <c r="Y27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="Z27" s="10">
+      <c r="Z27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AA27" s="10">
+      <c r="AA27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AB27" s="10">
+      <c r="AB27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AC27" s="10">
+      <c r="AC27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AD27" s="10">
+      <c r="AD27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AE27" s="10">
+      <c r="AE27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AF27" s="10">
+      <c r="AF27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AG27" s="10">
+      <c r="AG27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AH27" s="10">
+      <c r="AH27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AI27" s="10">
+      <c r="AI27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AJ27" s="10">
+      <c r="AJ27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AK27" s="10">
+      <c r="AK27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AL27" s="10">
+      <c r="AL27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AM27" s="10">
+      <c r="AM27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AN27" s="10">
+      <c r="AN27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AO27" s="10">
+      <c r="AO27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AP27" s="10">
+      <c r="AP27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AQ27" s="10">
+      <c r="AQ27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
-      <c r="AR27" s="10">
+      <c r="AR27" s="8">
         <f t="shared" si="2"/>
         <v>387.30224657894735</v>
       </c>
     </row>
-    <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="10">
+        <v>55</v>
+      </c>
+      <c r="C28" s="8">
         <f t="shared" ref="C28:AR28" si="3">IF(C23&gt;$B$19,-$B$15/$B$18,0)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="8">
         <f>IF(K23&gt;$B$19,-$B$15/$B$18,0)</f>
         <v>-11.105263157894736</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="O28" s="10">
+      <c r="O28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="P28" s="10">
+      <c r="P28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="Q28" s="10">
+      <c r="Q28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="R28" s="10">
+      <c r="R28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="S28" s="10">
+      <c r="S28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="T28" s="10">
+      <c r="T28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="U28" s="10">
+      <c r="U28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="V28" s="10">
+      <c r="V28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="W28" s="10">
+      <c r="W28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="X28" s="10">
+      <c r="X28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="Y28" s="10">
+      <c r="Y28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="Z28" s="10">
+      <c r="Z28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AA28" s="10">
+      <c r="AA28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AB28" s="10">
+      <c r="AB28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AC28" s="10">
+      <c r="AC28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AD28" s="10">
+      <c r="AD28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AE28" s="10">
+      <c r="AE28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AF28" s="10">
+      <c r="AF28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AG28" s="10">
+      <c r="AG28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AH28" s="10">
+      <c r="AH28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AI28" s="10">
+      <c r="AI28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AJ28" s="10">
+      <c r="AJ28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AK28" s="10">
+      <c r="AK28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AL28" s="10">
+      <c r="AL28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AM28" s="10">
+      <c r="AM28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AN28" s="10">
+      <c r="AN28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AO28" s="10">
+      <c r="AO28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AP28" s="10">
+      <c r="AP28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AQ28" s="10">
+      <c r="AQ28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
-      <c r="AR28" s="10">
+      <c r="AR28" s="8">
         <f t="shared" si="3"/>
         <v>-11.105263157894736</v>
       </c>
     </row>
-    <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="10">
+        <v>56</v>
+      </c>
+      <c r="C29" s="8">
         <f t="shared" ref="C29:AR29" si="4">C27+C28</f>
         <v>0</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="O29" s="10">
+      <c r="O29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="Q29" s="10">
+      <c r="Q29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="R29" s="10">
+      <c r="R29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="S29" s="10">
+      <c r="S29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="T29" s="10">
+      <c r="T29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="U29" s="10">
+      <c r="U29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="V29" s="10">
+      <c r="V29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="W29" s="10">
+      <c r="W29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="X29" s="10">
+      <c r="X29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="Y29" s="10">
+      <c r="Y29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="Z29" s="10">
+      <c r="Z29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AA29" s="10">
+      <c r="AA29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AB29" s="10">
+      <c r="AB29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AC29" s="10">
+      <c r="AC29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AD29" s="10">
+      <c r="AD29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AE29" s="10">
+      <c r="AE29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AF29" s="10">
+      <c r="AF29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AG29" s="10">
+      <c r="AG29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AH29" s="10">
+      <c r="AH29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AI29" s="10">
+      <c r="AI29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AJ29" s="10">
+      <c r="AJ29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AK29" s="10">
+      <c r="AK29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AL29" s="10">
+      <c r="AL29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AM29" s="10">
+      <c r="AM29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AN29" s="10">
+      <c r="AN29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AO29" s="10">
+      <c r="AO29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AP29" s="10">
+      <c r="AP29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AQ29" s="10">
+      <c r="AQ29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
-      <c r="AR29" s="10">
+      <c r="AR29" s="8">
         <f t="shared" si="4"/>
         <v>376.19698342105261</v>
       </c>
     </row>
-    <row r="30" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="10">
+        <v>57</v>
+      </c>
+      <c r="C30" s="8">
         <f t="shared" ref="C30:AR30" si="5">-MAX(C29,0)*$B$13</f>
         <v>0</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="R30" s="10">
+      <c r="R30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="S30" s="10">
+      <c r="S30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="T30" s="10">
+      <c r="T30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="U30" s="10">
+      <c r="U30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="V30" s="10">
+      <c r="V30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="W30" s="10">
+      <c r="W30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="X30" s="10">
+      <c r="X30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="Y30" s="10">
+      <c r="Y30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="Z30" s="10">
+      <c r="Z30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AA30" s="10">
+      <c r="AA30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AB30" s="10">
+      <c r="AB30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AC30" s="10">
+      <c r="AC30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AD30" s="10">
+      <c r="AD30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AE30" s="10">
+      <c r="AE30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AF30" s="10">
+      <c r="AF30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AG30" s="10">
+      <c r="AG30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AH30" s="10">
+      <c r="AH30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AI30" s="10">
+      <c r="AI30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AJ30" s="10">
+      <c r="AJ30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AK30" s="10">
+      <c r="AK30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AL30" s="10">
+      <c r="AL30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AM30" s="10">
+      <c r="AM30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AN30" s="10">
+      <c r="AN30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AO30" s="10">
+      <c r="AO30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AP30" s="10">
+      <c r="AP30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AQ30" s="10">
+      <c r="AQ30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
-      <c r="AR30" s="10">
+      <c r="AR30" s="8">
         <f t="shared" si="5"/>
         <v>-61.771544677736841</v>
       </c>
     </row>
-    <row r="31" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" s="10">
+        <v>58</v>
+      </c>
+      <c r="C31" s="8">
         <f t="shared" ref="C31:AR31" si="6">C29+C30</f>
         <v>0</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="O31" s="10">
+      <c r="O31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="Q31" s="10">
+      <c r="Q31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="R31" s="10">
+      <c r="R31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="S31" s="10">
+      <c r="S31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="T31" s="10">
+      <c r="T31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="U31" s="10">
+      <c r="U31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="V31" s="10">
+      <c r="V31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="W31" s="10">
+      <c r="W31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="X31" s="10">
+      <c r="X31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="Y31" s="10">
+      <c r="Y31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="Z31" s="10">
+      <c r="Z31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AA31" s="10">
+      <c r="AA31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AB31" s="10">
+      <c r="AB31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AC31" s="10">
+      <c r="AC31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AD31" s="10">
+      <c r="AD31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AE31" s="10">
+      <c r="AE31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AF31" s="10">
+      <c r="AF31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AG31" s="10">
+      <c r="AG31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AH31" s="10">
+      <c r="AH31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AI31" s="10">
+      <c r="AI31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AJ31" s="10">
+      <c r="AJ31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AK31" s="10">
+      <c r="AK31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AL31" s="10">
+      <c r="AL31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AM31" s="10">
+      <c r="AM31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AN31" s="10">
+      <c r="AN31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AO31" s="10">
+      <c r="AO31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AP31" s="10">
+      <c r="AP31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AQ31" s="10">
+      <c r="AQ31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AR31" s="10">
+      <c r="AR31" s="8">
         <f t="shared" si="6"/>
         <v>314.42543874331579</v>
       </c>
     </row>
-    <row r="32" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="10">
+        <v>59</v>
+      </c>
+      <c r="C32" s="8">
         <f t="shared" ref="C32:AR32" si="7">IF(C23&lt;=$B$19,-$B$14/$B$19,0)</f>
         <v>-285.25</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="8">
         <f t="shared" si="7"/>
         <v>-285.25</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="8">
         <f t="shared" si="7"/>
         <v>-285.25</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="8">
         <f t="shared" si="7"/>
         <v>-285.25</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M32" s="10">
+      <c r="M32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O32" s="10">
+      <c r="O32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P32" s="10">
+      <c r="P32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="10">
+      <c r="Q32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R32" s="10">
+      <c r="R32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S32" s="10">
+      <c r="S32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T32" s="10">
+      <c r="T32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U32" s="10">
+      <c r="U32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="V32" s="10">
+      <c r="V32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W32" s="10">
+      <c r="W32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="X32" s="10">
+      <c r="X32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Y32" s="10">
+      <c r="Y32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Z32" s="10">
+      <c r="Z32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="10">
+      <c r="AA32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB32" s="10">
+      <c r="AB32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC32" s="10">
+      <c r="AC32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD32" s="10">
+      <c r="AD32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AE32" s="10">
+      <c r="AE32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF32" s="10">
+      <c r="AF32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG32" s="10">
+      <c r="AG32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="10">
+      <c r="AH32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI32" s="10">
+      <c r="AI32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AJ32" s="10">
+      <c r="AJ32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK32" s="10">
+      <c r="AK32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL32" s="10">
+      <c r="AL32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM32" s="10">
+      <c r="AM32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="10">
+      <c r="AN32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AO32" s="10">
+      <c r="AO32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AP32" s="10">
+      <c r="AP32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AQ32" s="10">
+      <c r="AQ32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AR32" s="10">
+      <c r="AR32" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="10">
+        <v>60</v>
+      </c>
+      <c r="C33" s="8">
         <f t="shared" ref="C33:AR33" si="8">IF(C23=($B$18+$B$19),-$B$16,0)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M33" s="10">
+      <c r="M33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O33" s="10">
+      <c r="O33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P33" s="10">
+      <c r="P33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="10">
+      <c r="Q33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R33" s="10">
+      <c r="R33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S33" s="10">
+      <c r="S33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T33" s="10">
+      <c r="T33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U33" s="10">
+      <c r="U33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V33" s="10">
+      <c r="V33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W33" s="10">
+      <c r="W33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X33" s="10">
+      <c r="X33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Y33" s="10">
+      <c r="Y33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Z33" s="10">
+      <c r="Z33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA33" s="10">
+      <c r="AA33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AB33" s="10">
+      <c r="AB33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AC33" s="10">
+      <c r="AC33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AD33" s="10">
+      <c r="AD33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AE33" s="10">
+      <c r="AE33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF33" s="10">
+      <c r="AF33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AG33" s="10">
+      <c r="AG33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="10">
+      <c r="AH33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI33" s="10">
+      <c r="AI33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ33" s="10">
+      <c r="AJ33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK33" s="10">
+      <c r="AK33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="10">
+      <c r="AL33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AM33" s="10">
+      <c r="AM33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN33" s="10">
+      <c r="AN33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO33" s="10">
+      <c r="AO33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AP33" s="10">
+      <c r="AP33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AQ33" s="10">
+      <c r="AQ33" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AR33" s="10">
+      <c r="AR33" s="8">
         <f t="shared" si="8"/>
         <v>-44</v>
       </c>
     </row>
-    <row r="34" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="20">
+    <row r="34" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="13">
         <f t="shared" ref="C34:AR34" si="9">C31+C32+C33</f>
         <v>-285.25</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="13">
         <f t="shared" si="9"/>
         <v>-285.25</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="13">
         <f t="shared" si="9"/>
         <v>-285.25</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="13">
         <f t="shared" si="9"/>
         <v>-285.25</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="K34" s="20">
+      <c r="K34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="L34" s="20">
+      <c r="L34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="M34" s="20">
+      <c r="M34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="N34" s="20">
+      <c r="N34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="O34" s="20">
+      <c r="O34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="P34" s="20">
+      <c r="P34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="Q34" s="20">
+      <c r="Q34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="R34" s="20">
+      <c r="R34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="S34" s="20">
+      <c r="S34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="T34" s="20">
+      <c r="T34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="U34" s="20">
+      <c r="U34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="V34" s="20">
+      <c r="V34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="W34" s="20">
+      <c r="W34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="X34" s="20">
+      <c r="X34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="Y34" s="20">
+      <c r="Y34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="Z34" s="20">
+      <c r="Z34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AA34" s="20">
+      <c r="AA34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AB34" s="20">
+      <c r="AB34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AC34" s="20">
+      <c r="AC34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AE34" s="20">
+      <c r="AE34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AF34" s="20">
+      <c r="AF34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AG34" s="20">
+      <c r="AG34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AH34" s="20">
+      <c r="AH34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AI34" s="20">
+      <c r="AI34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AJ34" s="20">
+      <c r="AJ34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AK34" s="20">
+      <c r="AK34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AL34" s="20">
+      <c r="AL34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AM34" s="20">
+      <c r="AM34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AN34" s="20">
+      <c r="AN34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AO34" s="20">
+      <c r="AO34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AP34" s="20">
+      <c r="AP34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AQ34" s="20">
+      <c r="AQ34" s="13">
         <f t="shared" si="9"/>
         <v>314.42543874331579</v>
       </c>
-      <c r="AR34" s="20">
+      <c r="AR34" s="13">
         <f t="shared" si="9"/>
         <v>270.42543874331579</v>
       </c>
     </row>
-    <row r="35" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="32">
+        <v>62</v>
+      </c>
+      <c r="C35" s="22">
         <f t="shared" ref="C35:AR35" si="10">1/(1+$B$17)^C23</f>
         <v>0.92592592592592582</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="22">
         <f t="shared" si="10"/>
         <v>0.85733882030178321</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="22">
         <f t="shared" si="10"/>
         <v>0.79383224102016958</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="22">
         <f t="shared" si="10"/>
         <v>0.73502985279645328</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="22">
         <f t="shared" si="10"/>
         <v>0.68058319703375303</v>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="22">
         <f t="shared" si="10"/>
         <v>0.63016962688310452</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="22">
         <f t="shared" si="10"/>
         <v>0.58349039526213387</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="22">
         <f t="shared" si="10"/>
         <v>0.54026888450197574</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="22">
         <f t="shared" si="10"/>
         <v>0.50024896713145905</v>
       </c>
-      <c r="L35" s="32">
+      <c r="L35" s="22">
         <f t="shared" si="10"/>
         <v>0.46319348808468425</v>
       </c>
-      <c r="M35" s="32">
+      <c r="M35" s="22">
         <f t="shared" si="10"/>
         <v>0.42888285933767062</v>
       </c>
-      <c r="N35" s="32">
+      <c r="N35" s="22">
         <f t="shared" si="10"/>
         <v>0.39711375864599124</v>
       </c>
-      <c r="O35" s="32">
+      <c r="O35" s="22">
         <f t="shared" si="10"/>
         <v>0.36769792467221413</v>
       </c>
-      <c r="P35" s="32">
+      <c r="P35" s="22">
         <f t="shared" si="10"/>
         <v>0.34046104136316119</v>
       </c>
-      <c r="Q35" s="32">
+      <c r="Q35" s="22">
         <f t="shared" si="10"/>
         <v>0.31524170496588994</v>
       </c>
-      <c r="R35" s="32">
+      <c r="R35" s="22">
         <f t="shared" si="10"/>
         <v>0.29189046756100923</v>
       </c>
-      <c r="S35" s="32">
+      <c r="S35" s="22">
         <f t="shared" si="10"/>
         <v>0.27026895144537894</v>
       </c>
-      <c r="T35" s="32">
+      <c r="T35" s="22">
         <f t="shared" si="10"/>
         <v>0.25024902911609154</v>
       </c>
-      <c r="U35" s="32">
+      <c r="U35" s="22">
         <f t="shared" si="10"/>
         <v>0.23171206399638106</v>
       </c>
-      <c r="V35" s="32">
+      <c r="V35" s="22">
         <f t="shared" si="10"/>
         <v>0.21454820740405653</v>
       </c>
-      <c r="W35" s="32">
+      <c r="W35" s="22">
         <f t="shared" si="10"/>
         <v>0.19865574759634863</v>
       </c>
-      <c r="X35" s="32">
+      <c r="X35" s="22">
         <f t="shared" si="10"/>
         <v>0.18394050703365611</v>
       </c>
-      <c r="Y35" s="32">
+      <c r="Y35" s="22">
         <f t="shared" si="10"/>
         <v>0.17031528429042234</v>
       </c>
-      <c r="Z35" s="32">
+      <c r="Z35" s="22">
         <f t="shared" si="10"/>
         <v>0.1576993373059466</v>
       </c>
-      <c r="AA35" s="32">
+      <c r="AA35" s="22">
         <f t="shared" si="10"/>
         <v>0.1460179049129135</v>
       </c>
-      <c r="AB35" s="32">
+      <c r="AB35" s="22">
         <f t="shared" si="10"/>
         <v>0.13520176380825324</v>
       </c>
-      <c r="AC35" s="32">
+      <c r="AC35" s="22">
         <f t="shared" si="10"/>
         <v>0.12518681834097523</v>
       </c>
-      <c r="AD35" s="32">
+      <c r="AD35" s="22">
         <f t="shared" si="10"/>
         <v>0.11591372068608817</v>
       </c>
-      <c r="AE35" s="32">
+      <c r="AE35" s="22">
         <f t="shared" si="10"/>
         <v>0.10732751915378534</v>
       </c>
-      <c r="AF35" s="32">
+      <c r="AF35" s="22">
         <f t="shared" si="10"/>
         <v>9.9377332549801231E-2</v>
       </c>
-      <c r="AG35" s="32">
+      <c r="AG35" s="22">
         <f t="shared" si="10"/>
         <v>9.2016048657223348E-2</v>
       </c>
-      <c r="AH35" s="32">
+      <c r="AH35" s="22">
         <f t="shared" si="10"/>
         <v>8.5200045052984577E-2</v>
       </c>
-      <c r="AI35" s="32">
+      <c r="AI35" s="22">
         <f t="shared" si="10"/>
         <v>7.8888930604615354E-2</v>
       </c>
-      <c r="AJ35" s="32">
+      <c r="AJ35" s="22">
         <f t="shared" si="10"/>
         <v>7.3045306115384581E-2</v>
       </c>
-      <c r="AK35" s="32">
+      <c r="AK35" s="22">
         <f t="shared" si="10"/>
         <v>6.7634542699430159E-2</v>
       </c>
-      <c r="AL35" s="32">
+      <c r="AL35" s="22">
         <f t="shared" si="10"/>
         <v>6.2624576573546434E-2</v>
       </c>
-      <c r="AM35" s="32">
+      <c r="AM35" s="22">
         <f t="shared" si="10"/>
         <v>5.7985719049580033E-2</v>
       </c>
-      <c r="AN35" s="32">
+      <c r="AN35" s="22">
         <f t="shared" si="10"/>
         <v>5.3690480601462989E-2</v>
       </c>
-      <c r="AO35" s="32">
+      <c r="AO35" s="22">
         <f t="shared" si="10"/>
         <v>4.9713407964317585E-2</v>
       </c>
-      <c r="AP35" s="32">
+      <c r="AP35" s="22">
         <f t="shared" si="10"/>
         <v>4.6030933300294057E-2</v>
       </c>
-      <c r="AQ35" s="32">
+      <c r="AQ35" s="22">
         <f t="shared" si="10"/>
         <v>4.2621234537309309E-2</v>
       </c>
-      <c r="AR35" s="32">
+      <c r="AR35" s="22">
         <f t="shared" si="10"/>
         <v>3.9464106053064177E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="20">
+    <row r="36" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="13">
         <f t="shared" ref="C36:AR36" si="11">C34*C35</f>
         <v>-264.12037037037032</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="13">
         <f t="shared" si="11"/>
         <v>-244.55589849108367</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="13">
         <f t="shared" si="11"/>
         <v>-226.44064675100338</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="13">
         <f t="shared" si="11"/>
         <v>-209.66726551018829</v>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="13">
         <f t="shared" si="11"/>
         <v>213.99267032866635</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="13">
         <f t="shared" si="11"/>
         <v>198.14136141543176</v>
       </c>
-      <c r="I36" s="20">
+      <c r="I36" s="13">
         <f t="shared" si="11"/>
         <v>183.46422353280718</v>
       </c>
-      <c r="J36" s="20">
+      <c r="J36" s="13">
         <f t="shared" si="11"/>
         <v>169.87428104889554</v>
       </c>
-      <c r="K36" s="20">
+      <c r="K36" s="13">
         <f t="shared" si="11"/>
         <v>157.29100097119957</v>
       </c>
-      <c r="L36" s="20">
+      <c r="L36" s="13">
         <f t="shared" si="11"/>
         <v>145.63981571407365</v>
       </c>
-      <c r="M36" s="20">
+      <c r="M36" s="13">
         <f t="shared" si="11"/>
         <v>134.85168121673487</v>
       </c>
-      <c r="N36" s="20">
+      <c r="N36" s="13">
         <f t="shared" si="11"/>
         <v>124.86266779327302</v>
       </c>
-      <c r="O36" s="20">
+      <c r="O36" s="13">
         <f t="shared" si="11"/>
         <v>115.61358129006761</v>
       </c>
-      <c r="P36" s="20">
+      <c r="P36" s="13">
         <f t="shared" si="11"/>
         <v>107.04961230561814</v>
       </c>
-      <c r="Q36" s="20">
+      <c r="Q36" s="13">
         <f t="shared" si="11"/>
         <v>99.120011394090852</v>
       </c>
-      <c r="R36" s="20">
+      <c r="R36" s="13">
         <f t="shared" si="11"/>
         <v>91.777788327861913</v>
       </c>
-      <c r="S36" s="20">
+      <c r="S36" s="13">
         <f t="shared" si="11"/>
         <v>84.979433636909192</v>
       </c>
-      <c r="T36" s="20">
+      <c r="T36" s="13">
         <f t="shared" si="11"/>
         <v>78.684660774915884</v>
       </c>
-      <c r="U36" s="20">
+      <c r="U36" s="13">
         <f t="shared" si="11"/>
         <v>72.856167384181376</v>
       </c>
-      <c r="V36" s="20">
+      <c r="V36" s="13">
         <f t="shared" si="11"/>
         <v>67.45941424461239</v>
       </c>
-      <c r="W36" s="20">
+      <c r="W36" s="13">
         <f t="shared" si="11"/>
         <v>62.462420596863318</v>
       </c>
-      <c r="X36" s="20">
+      <c r="X36" s="13">
         <f t="shared" si="11"/>
         <v>57.83557462672529</v>
       </c>
-      <c r="Y36" s="20">
+      <c r="Y36" s="13">
         <f t="shared" si="11"/>
         <v>53.551457987708602</v>
       </c>
-      <c r="Z36" s="20">
+      <c r="Z36" s="13">
         <f t="shared" si="11"/>
         <v>49.584683321952404</v>
       </c>
-      <c r="AA36" s="20">
+      <c r="AA36" s="13">
         <f t="shared" si="11"/>
         <v>45.911743816622597</v>
       </c>
-      <c r="AB36" s="20">
+      <c r="AB36" s="13">
         <f t="shared" si="11"/>
         <v>42.510873904280182</v>
       </c>
-      <c r="AC36" s="20">
+      <c r="AC36" s="13">
         <f t="shared" si="11"/>
         <v>39.361920281740908</v>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="13">
         <f t="shared" si="11"/>
         <v>36.446222483093436</v>
       </c>
-      <c r="AE36" s="20">
+      <c r="AE36" s="13">
         <f t="shared" si="11"/>
         <v>33.746502299160582</v>
       </c>
-      <c r="AF36" s="20">
+      <c r="AF36" s="13">
         <f t="shared" si="11"/>
         <v>31.246761388111651</v>
       </c>
-      <c r="AG36" s="20">
+      <c r="AG36" s="13">
         <f t="shared" si="11"/>
         <v>28.932186470473745</v>
       </c>
-      <c r="AH36" s="20">
+      <c r="AH36" s="13">
         <f t="shared" si="11"/>
         <v>26.789061546734949</v>
       </c>
-      <c r="AI36" s="20">
+      <c r="AI36" s="13">
         <f t="shared" si="11"/>
         <v>24.804686617347176</v>
       </c>
-      <c r="AJ36" s="20">
+      <c r="AJ36" s="13">
         <f t="shared" si="11"/>
         <v>22.967302423469604</v>
       </c>
-      <c r="AK36" s="20">
+      <c r="AK36" s="13">
         <f t="shared" si="11"/>
         <v>21.266020762471854</v>
       </c>
-      <c r="AL36" s="20">
+      <c r="AL36" s="13">
         <f t="shared" si="11"/>
         <v>19.690759965251715</v>
       </c>
-      <c r="AM36" s="20">
+      <c r="AM36" s="13">
         <f t="shared" si="11"/>
         <v>18.232185153010846</v>
       </c>
-      <c r="AN36" s="20">
+      <c r="AN36" s="13">
         <f t="shared" si="11"/>
         <v>16.881652919454485</v>
       </c>
-      <c r="AO36" s="20">
+      <c r="AO36" s="13">
         <f t="shared" si="11"/>
         <v>15.631160110606006</v>
       </c>
-      <c r="AP36" s="20">
+      <c r="AP36" s="13">
         <f t="shared" si="11"/>
         <v>14.473296398709264</v>
       </c>
-      <c r="AQ36" s="20">
+      <c r="AQ36" s="13">
         <f t="shared" si="11"/>
         <v>13.401200369175244</v>
       </c>
-      <c r="AR36" s="20">
+      <c r="AR36" s="13">
         <f t="shared" si="11"/>
         <v>10.672098194012625</v>
       </c>
     </row>
-    <row r="39" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="20">
+        <v>65</v>
+      </c>
+      <c r="B40" s="13">
         <f>SUM(C36:AR36)</f>
         <v>1787.27396189367</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B41" s="11">
+        <v>105</v>
+      </c>
+      <c r="B41" s="41">
         <f>Assumptions!$B$23</f>
         <v>2350</v>
       </c>
     </row>
-    <row r="42" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B42" s="10">
+        <v>106</v>
+      </c>
+      <c r="B42" s="8">
         <f>B40-B41</f>
         <v>-562.72603810632995</v>
       </c>
     </row>
-    <row r="43" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" s="14">
+        <v>66</v>
+      </c>
+      <c r="B43" s="10">
         <f>B40/B41</f>
         <v>0.76054211144411488</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="88.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="8">
-        <f>Main!B2</f>
-        <v>4.57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="48">
-        <f>Main!B3</f>
-        <v>45.072000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="10">
-        <f>B4*B5</f>
-        <v>205.97904000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="11">
-        <f>Main!B6-Main!B5</f>
-        <v>-10.84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="11">
-        <f>NAV!$B$41</f>
-        <v>2350</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="11">
-        <f>NAV!$B$40</f>
-        <v>1787.27396189367</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="11">
-        <f>Assumptions!$B$17</f>
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="14">
-        <f>1-B15</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="10">
-        <f>B14*B15</f>
-        <v>570.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="15">
-        <f>Main!B2</f>
-        <v>4.57</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="16">
-        <f>B17/B18</f>
-        <v>124.835886214442</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="17">
-        <f>Assumptions!$B$29</f>
-        <v>33.005921999999998</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="18">
-        <f>B5+B19+B20</f>
-        <v>202.91380821444199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="10">
-        <f>B10</f>
-        <v>2350</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="19">
-        <f>Assumptions!$B$28</f>
-        <v>25.5</v>
-      </c>
-      <c r="D25" s="12"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="10">
-        <f>-B7</f>
-        <v>10.84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="20">
-        <f>B24+B25+B26</f>
-        <v>2386.34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="21">
-        <f>B27/B21</f>
-        <v>11.760362791467028</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="22">
-        <f>B4</f>
-        <v>4.57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="23">
-        <f>B28/B29-1</f>
-        <v>1.5733835429905967</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-    </row>
-    <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="22">
-        <f>0.3*B28</f>
-        <v>3.5281088374401084</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="22">
-        <f>0.5*B28</f>
-        <v>5.8801813957335138</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="22">
-        <f>0.7*B28</f>
-        <v>8.2322539540269197</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="24">
-        <f>B29/B28</f>
-        <v>0.38859345421859415</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3994,856 +3908,297 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="11" width="12" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="18.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="11">
-        <f>NAV!D6</f>
-        <v>13505.624</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="11">
-        <f>NAV!D7</f>
-        <v>427.47507000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="B4" s="31">
+        <f>Main!B2</f>
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="11">
-        <f>NAV!B11</f>
-        <v>7182.1806999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="B5" s="35">
+        <f>Main!B3</f>
+        <v>45.072000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="27">
-        <f>NAV!B13</f>
-        <v>0.16420000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8">
+        <f>B4*B5</f>
+        <v>205.97904000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="11">
-        <f>NAV!B15</f>
-        <v>422</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="11">
-        <f>NAV!B14</f>
+        <v>9</v>
+      </c>
+      <c r="B7" s="33">
+        <f>Main!B6-Main!B5</f>
+        <v>-10.84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="33">
+        <f>NAV!$B$41</f>
+        <v>2350</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="33">
+        <f>NAV!$B$40</f>
+        <v>1787.27396189367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="33">
+        <f>Assumptions!$B$17</f>
         <v>1141</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="11">
-        <f>NAV!B16</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="9">
-        <f>NAV!B18</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="9">
-        <f>NAV!B19</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="9">
-        <f>NAV!B5</f>
-        <v>171140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="9">
-        <f>Valuation!B21</f>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10">
+        <f>1-B15</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8">
+        <f>B14*B15</f>
+        <v>570.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="37">
+        <f>Main!B2</f>
+        <v>4.57</v>
+      </c>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="11">
+        <f>B17/B18</f>
+        <v>124.835886214442</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="38">
+        <f>Assumptions!$B$29</f>
+        <v>33.005921999999998</v>
+      </c>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12">
+        <f>B5+B19+B20</f>
         <v>202.91380821444199</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="34">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="8">
+        <f>B10</f>
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="37">
+        <f>Assumptions!$B$28</f>
+        <v>25.5</v>
+      </c>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8">
+        <f>-B7</f>
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="13">
+        <f>B24+B25+B26</f>
+        <v>2386.34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="39">
+        <f>B27/B21</f>
+        <v>11.760362791467028</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="14">
+        <f>B4</f>
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="15">
+        <f>B28/B29-1</f>
+        <v>1.5733835429905967</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="40">
+        <f>0.3*B28</f>
+        <v>3.5281088374401084</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="40">
+        <f>0.5*B28</f>
+        <v>5.8801813957335138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="34">
-        <v>40</v>
-      </c>
-      <c r="D18" s="34">
-        <v>46.55</v>
-      </c>
-      <c r="E18" s="34">
-        <v>55</v>
-      </c>
-      <c r="F18" s="34">
-        <v>65</v>
-      </c>
-      <c r="G18" s="34">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="35">
-        <v>0.06</v>
-      </c>
-      <c r="B19" s="36">
-        <f t="shared" ref="B19:G24" si="0">((($B$12*B$18/1000+$B$3+$B$4-$B$5)/$B$10-$B$7/$B$10)*(1-$B$6))*(((1-POWER(1+$A19,-($B$10+$B$11)))/$A19)-((1-POWER(1+$A19,-$B$11))/$A19))-($B$8/$B$11)*((1-POWER(1+$A19,-$B$11))/$A19)-$B$9*POWER(1+$A19,-($B$10+$B$11))</f>
-        <v>1972.6581258060094</v>
-      </c>
-      <c r="C19" s="36">
-        <f t="shared" si="0"/>
-        <v>2415.3044413534685</v>
-      </c>
-      <c r="D19" s="36">
-        <f t="shared" si="0"/>
-        <v>2705.2377780370534</v>
-      </c>
-      <c r="E19" s="36">
-        <f t="shared" si="0"/>
-        <v>3079.2739146746571</v>
-      </c>
-      <c r="F19" s="36">
-        <f t="shared" si="0"/>
-        <v>3521.9202302221161</v>
-      </c>
-      <c r="G19" s="36">
-        <f t="shared" si="0"/>
-        <v>3964.5665457695745</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="B20" s="36">
-        <f t="shared" si="0"/>
-        <v>1568.9625270447289</v>
-      </c>
-      <c r="C20" s="36">
-        <f t="shared" si="0"/>
-        <v>1947.8361184003554</v>
-      </c>
-      <c r="D20" s="36">
-        <f t="shared" si="0"/>
-        <v>2195.9983207382902</v>
-      </c>
-      <c r="E20" s="36">
-        <f t="shared" si="0"/>
-        <v>2516.146505433795</v>
-      </c>
-      <c r="F20" s="36">
-        <f t="shared" si="0"/>
-        <v>2895.0200967894216</v>
-      </c>
-      <c r="G20" s="36">
-        <f t="shared" si="0"/>
-        <v>3273.8936881450481</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="35">
-        <v>0.08</v>
-      </c>
-      <c r="B21" s="36">
-        <f t="shared" si="0"/>
-        <v>1245.6267700324177</v>
-      </c>
-      <c r="C21" s="36">
-        <f t="shared" si="0"/>
-        <v>1572.9060400392175</v>
-      </c>
-      <c r="D21" s="37">
-        <f t="shared" si="0"/>
-        <v>1787.273961893671</v>
-      </c>
-      <c r="E21" s="36">
-        <f t="shared" si="0"/>
-        <v>2063.8249450494181</v>
-      </c>
-      <c r="F21" s="36">
-        <f t="shared" si="0"/>
-        <v>2391.104215056218</v>
-      </c>
-      <c r="G21" s="36">
-        <f t="shared" si="0"/>
-        <v>2718.3834850630183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="35">
-        <v>0.09</v>
-      </c>
-      <c r="B22" s="36">
-        <f t="shared" si="0"/>
-        <v>984.22115459433837</v>
-      </c>
-      <c r="C22" s="36">
-        <f t="shared" si="0"/>
-        <v>1269.3067730236191</v>
-      </c>
-      <c r="D22" s="36">
-        <f t="shared" si="0"/>
-        <v>1456.0378530947971</v>
-      </c>
-      <c r="E22" s="36">
-        <f t="shared" si="0"/>
-        <v>1696.9352006675397</v>
-      </c>
-      <c r="F22" s="36">
-        <f t="shared" si="0"/>
-        <v>1982.0208190968199</v>
-      </c>
-      <c r="G22" s="36">
-        <f t="shared" si="0"/>
-        <v>2267.1064375261003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="35">
-        <v>0.1</v>
-      </c>
-      <c r="B23" s="36">
-        <f t="shared" si="0"/>
-        <v>771.0231453842548</v>
-      </c>
-      <c r="C23" s="36">
-        <f t="shared" si="0"/>
-        <v>1021.2481604794327</v>
-      </c>
-      <c r="D23" s="36">
-        <f t="shared" si="0"/>
-        <v>1185.1455453667736</v>
-      </c>
-      <c r="E23" s="36">
-        <f t="shared" si="0"/>
-        <v>1396.5856831221995</v>
-      </c>
-      <c r="F23" s="36">
-        <f t="shared" si="0"/>
-        <v>1646.8106982173772</v>
-      </c>
-      <c r="G23" s="36">
-        <f t="shared" si="0"/>
-        <v>1897.0357133125549</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="35">
-        <v>0.12</v>
-      </c>
-      <c r="B24" s="36">
-        <f t="shared" si="0"/>
-        <v>450.48597981100755</v>
-      </c>
-      <c r="C24" s="36">
-        <f t="shared" si="0"/>
-        <v>647.14891213793965</v>
-      </c>
-      <c r="D24" s="36">
-        <f t="shared" si="0"/>
-        <v>775.96313281208006</v>
-      </c>
-      <c r="E24" s="36">
-        <f t="shared" si="0"/>
-        <v>942.14331062833833</v>
-      </c>
-      <c r="F24" s="36">
-        <f t="shared" si="0"/>
-        <v>1138.8062429552704</v>
-      </c>
-      <c r="G24" s="36">
-        <f t="shared" si="0"/>
-        <v>1335.469175282203</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="34">
-        <v>30</v>
-      </c>
-      <c r="C28" s="34">
-        <v>40</v>
-      </c>
-      <c r="D28" s="34">
-        <v>46.55</v>
-      </c>
-      <c r="E28" s="34">
-        <v>55</v>
-      </c>
-      <c r="F28" s="34">
-        <v>65</v>
-      </c>
-      <c r="G28" s="34">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35">
-        <v>0.06</v>
-      </c>
-      <c r="B29" s="38">
-        <f t="shared" ref="B29:G34" si="1">B19/$B$13</f>
-        <v>9.721655431754936</v>
-      </c>
-      <c r="C29" s="38">
-        <f t="shared" si="1"/>
-        <v>11.903105375662474</v>
-      </c>
-      <c r="D29" s="38">
-        <f t="shared" si="1"/>
-        <v>13.331955088921905</v>
-      </c>
-      <c r="E29" s="38">
-        <f t="shared" si="1"/>
-        <v>15.175280291523778</v>
-      </c>
-      <c r="F29" s="38">
-        <f t="shared" si="1"/>
-        <v>17.356730235431314</v>
-      </c>
-      <c r="G29" s="38">
-        <f t="shared" si="1"/>
-        <v>19.538180179338848</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="35">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="B30" s="38">
-        <f t="shared" si="1"/>
-        <v>7.7321624430143689</v>
-      </c>
-      <c r="C30" s="38">
-        <f t="shared" si="1"/>
-        <v>9.5993275940189182</v>
-      </c>
-      <c r="D30" s="38">
-        <f t="shared" si="1"/>
-        <v>10.822320767926893</v>
-      </c>
-      <c r="E30" s="38">
-        <f t="shared" si="1"/>
-        <v>12.400075320525739</v>
-      </c>
-      <c r="F30" s="38">
-        <f t="shared" si="1"/>
-        <v>14.267240471530288</v>
-      </c>
-      <c r="G30" s="38">
-        <f t="shared" si="1"/>
-        <v>16.134405622534835</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35">
-        <v>0.08</v>
-      </c>
-      <c r="B31" s="38">
-        <f t="shared" si="1"/>
-        <v>6.1386988938476916</v>
-      </c>
-      <c r="C31" s="38">
-        <f t="shared" si="1"/>
-        <v>7.7515968670646096</v>
-      </c>
-      <c r="D31" s="39">
-        <f t="shared" si="1"/>
-        <v>8.8080450395216889</v>
-      </c>
-      <c r="E31" s="38">
-        <f t="shared" si="1"/>
-        <v>10.170943826889991</v>
-      </c>
-      <c r="F31" s="38">
-        <f t="shared" si="1"/>
-        <v>11.783841800106908</v>
-      </c>
-      <c r="G31" s="38">
-        <f t="shared" si="1"/>
-        <v>13.396739773323828</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="35">
-        <v>0.09</v>
-      </c>
-      <c r="B32" s="38">
-        <f t="shared" si="1"/>
-        <v>4.8504395203809914</v>
-      </c>
-      <c r="C32" s="38">
-        <f t="shared" si="1"/>
-        <v>6.2553987044696289</v>
-      </c>
-      <c r="D32" s="38">
-        <f t="shared" si="1"/>
-        <v>7.1756469700476826</v>
-      </c>
-      <c r="E32" s="38">
-        <f t="shared" si="1"/>
-        <v>8.3628374806025825</v>
-      </c>
-      <c r="F32" s="38">
-        <f t="shared" si="1"/>
-        <v>9.7677966646912182</v>
-      </c>
-      <c r="G32" s="38">
-        <f t="shared" si="1"/>
-        <v>11.172755848779854</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35">
-        <v>0.1</v>
-      </c>
-      <c r="B33" s="38">
-        <f t="shared" si="1"/>
-        <v>3.7997569124001034</v>
-      </c>
-      <c r="C33" s="38">
-        <f t="shared" si="1"/>
-        <v>5.0329160418701733</v>
-      </c>
-      <c r="D33" s="38">
-        <f t="shared" si="1"/>
-        <v>5.8406352716730652</v>
-      </c>
-      <c r="E33" s="38">
-        <f t="shared" si="1"/>
-        <v>6.8826547360752768</v>
-      </c>
-      <c r="F33" s="38">
-        <f t="shared" si="1"/>
-        <v>8.1158138655453449</v>
-      </c>
-      <c r="G33" s="38">
-        <f t="shared" si="1"/>
-        <v>9.3489729950154139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35">
-        <v>0.12</v>
-      </c>
-      <c r="B34" s="38">
-        <f t="shared" si="1"/>
-        <v>2.2200853839129966</v>
-      </c>
-      <c r="C34" s="38">
-        <f t="shared" si="1"/>
-        <v>3.1892798121162071</v>
-      </c>
-      <c r="D34" s="38">
-        <f t="shared" si="1"/>
-        <v>3.8241021625893099</v>
-      </c>
-      <c r="E34" s="38">
-        <f t="shared" si="1"/>
-        <v>4.6430714544210261</v>
-      </c>
-      <c r="F34" s="38">
-        <f t="shared" si="1"/>
-        <v>5.6122658826242366</v>
-      </c>
-      <c r="G34" s="38">
-        <f t="shared" si="1"/>
-        <v>6.5814603108274499</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="45"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="45"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="43">
-        <v>36655</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="43">
-        <v>38</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="43">
-        <v>4</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="43">
-        <v>171140</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="43">
-        <v>3676</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="43">
-        <v>431793</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="46">
-        <v>46.55</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="46">
-        <v>3674</v>
-      </c>
-      <c r="C13" s="44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="46">
-        <v>0.99</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="46">
-        <v>195.94</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="43">
-        <v>1141</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="43">
-        <v>422</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="43">
-        <v>44</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="47">
-        <v>0.16420000000000001</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="47">
-        <v>0.08</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" s="43">
-        <v>2350</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" s="47">
-        <v>0.27600000000000002</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="43">
-        <v>2800</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="47">
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B28" s="46">
-        <f>Main!B5</f>
-        <v>25.5</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" s="43">
-        <f>(29985922+3020000)/1000000</f>
-        <v>33.005921999999998</v>
-      </c>
-      <c r="C29" s="44" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B30" s="43"/>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
+      <c r="B35" s="40">
+        <f>0.7*B28</f>
+        <v>8.2322539540269197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="16">
+        <f>B29/B28</f>
+        <v>0.38859345421859415</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
